--- a/public/templates/forms/A-156-ScreeningCompletionRecords-FORM.xlsx
+++ b/public/templates/forms/A-156-ScreeningCompletionRecords-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -585,7 +588,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage</t>
@@ -615,7 +618,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -734,7 +737,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="29.75" customHeight="1">
+    <row r="24" ht="34.7" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>« Summarize coverage: how many required personnel are current, how many pending, and any overdue for re-screening. Mirror overdue items into the Risk / Finding Register (POA&amp;M). »</t>
@@ -961,7 +964,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -987,14 +990,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template (delete this sheet's notes before publishing): this is the Screening Completion Records register. Fill the header block on the Log tab, replace every [BRACKETED] field, add rows as people are screened, then delete every « » note before publishing.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, completion summary, sign-off, retention and revision history live on the Log tab.</t>
@@ -1052,7 +1055,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Name &amp; Position</t>
@@ -1074,7 +1077,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Screening checks completed</t>
@@ -1096,7 +1099,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Clearance status &amp; date</t>
@@ -1118,7 +1121,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Verified / adjudicated by (role)</t>
@@ -1140,7 +1143,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Access granted · Re-screen due</t>
@@ -1237,6 +1240,6 @@
     <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>